--- a/Additional_Materials/Charakterystyka_dokladna.xlsx
+++ b/Additional_Materials/Charakterystyka_dokladna.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Konrad\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Studia\10th_semester\Master_Thesis\Github_Repository\PDLC_Master\Additional_Materials\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C27142CA-2F00-4848-8E26-7015E0F68017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CharakterystykaD" sheetId="1" r:id="rId1"/>
@@ -330,17 +330,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -352,6 +349,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -638,28 +638,28 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="D1" s="15" t="s">
+      <c r="B1" s="16"/>
+      <c r="D1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="15"/>
+      <c r="E1" s="16"/>
       <c r="F1" t="s">
         <v>0</v>
       </c>
       <c r="G1">
         <v>139</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="15"/>
-      <c r="L1" s="15" t="s">
+      <c r="J1" s="16"/>
+      <c r="L1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="M1" s="15"/>
+      <c r="M1" s="16"/>
       <c r="P1" t="s">
         <v>0</v>
       </c>
@@ -1448,126 +1448,126 @@
       <c r="E42" s="1"/>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A47" s="16" t="s">
+      <c r="A47" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="B47" s="16"/>
-      <c r="C47" s="16"/>
-      <c r="D47" s="16"/>
-      <c r="E47" s="16"/>
-      <c r="F47" s="16"/>
-      <c r="G47" s="16" t="s">
+      <c r="B47" s="14"/>
+      <c r="C47" s="14"/>
+      <c r="D47" s="14"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="14"/>
+      <c r="G47" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="H47" s="16"/>
-      <c r="I47" s="16"/>
-      <c r="J47" s="16"/>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16" t="s">
+      <c r="H47" s="14"/>
+      <c r="I47" s="14"/>
+      <c r="J47" s="14"/>
+      <c r="K47" s="14"/>
+      <c r="L47" s="14"/>
+      <c r="M47" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="N47" s="16"/>
-      <c r="O47" s="16"/>
-      <c r="P47" s="16"/>
-      <c r="Q47" s="16"/>
-      <c r="R47" s="16"/>
+      <c r="N47" s="14"/>
+      <c r="O47" s="14"/>
+      <c r="P47" s="14"/>
+      <c r="Q47" s="14"/>
+      <c r="R47" s="14"/>
       <c r="S47" s="3"/>
       <c r="T47" s="3"/>
     </row>
     <row r="48" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="17" t="s">
+      <c r="A48" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="B48" s="17"/>
-      <c r="C48" s="17"/>
-      <c r="D48" s="17"/>
-      <c r="E48" s="17"/>
-      <c r="F48" s="17"/>
-      <c r="G48" s="17" t="s">
+      <c r="B48" s="15"/>
+      <c r="C48" s="15"/>
+      <c r="D48" s="15"/>
+      <c r="E48" s="15"/>
+      <c r="F48" s="15"/>
+      <c r="G48" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="H48" s="17"/>
-      <c r="I48" s="17"/>
-      <c r="J48" s="17"/>
-      <c r="K48" s="17"/>
-      <c r="L48" s="17"/>
-      <c r="M48" s="17" t="s">
+      <c r="H48" s="15"/>
+      <c r="I48" s="15"/>
+      <c r="J48" s="15"/>
+      <c r="K48" s="15"/>
+      <c r="L48" s="15"/>
+      <c r="M48" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="N48" s="17"/>
-      <c r="O48" s="17"/>
-      <c r="P48" s="17"/>
-      <c r="Q48" s="17"/>
-      <c r="R48" s="17"/>
-      <c r="S48" s="16" t="s">
+      <c r="N48" s="15"/>
+      <c r="O48" s="15"/>
+      <c r="P48" s="15"/>
+      <c r="Q48" s="15"/>
+      <c r="R48" s="15"/>
+      <c r="S48" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="T48" s="16"/>
+      <c r="T48" s="14"/>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A49" s="17"/>
-      <c r="B49" s="17"/>
-      <c r="C49" s="17"/>
-      <c r="D49" s="17"/>
-      <c r="E49" s="17"/>
-      <c r="F49" s="17"/>
-      <c r="G49" s="17"/>
-      <c r="H49" s="17"/>
-      <c r="I49" s="17"/>
-      <c r="J49" s="17"/>
-      <c r="K49" s="17"/>
-      <c r="L49" s="17"/>
-      <c r="M49" s="17"/>
-      <c r="N49" s="17"/>
-      <c r="O49" s="17"/>
-      <c r="P49" s="17"/>
-      <c r="Q49" s="17"/>
-      <c r="R49" s="17"/>
-      <c r="S49" s="16"/>
-      <c r="T49" s="16"/>
+      <c r="A49" s="15"/>
+      <c r="B49" s="15"/>
+      <c r="C49" s="15"/>
+      <c r="D49" s="15"/>
+      <c r="E49" s="15"/>
+      <c r="F49" s="15"/>
+      <c r="G49" s="15"/>
+      <c r="H49" s="15"/>
+      <c r="I49" s="15"/>
+      <c r="J49" s="15"/>
+      <c r="K49" s="15"/>
+      <c r="L49" s="15"/>
+      <c r="M49" s="15"/>
+      <c r="N49" s="15"/>
+      <c r="O49" s="15"/>
+      <c r="P49" s="15"/>
+      <c r="Q49" s="15"/>
+      <c r="R49" s="15"/>
+      <c r="S49" s="14"/>
+      <c r="T49" s="14"/>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A50" s="16" t="s">
+      <c r="A50" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="B50" s="16"/>
-      <c r="C50" s="16" t="s">
+      <c r="B50" s="14"/>
+      <c r="C50" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="D50" s="16"/>
-      <c r="E50" s="16" t="s">
+      <c r="D50" s="14"/>
+      <c r="E50" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F50" s="16"/>
-      <c r="G50" s="16" t="s">
+      <c r="F50" s="14"/>
+      <c r="G50" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="H50" s="16"/>
-      <c r="I50" s="16" t="s">
+      <c r="H50" s="14"/>
+      <c r="I50" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="J50" s="16"/>
-      <c r="K50" s="16" t="s">
+      <c r="J50" s="14"/>
+      <c r="K50" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16" t="s">
+      <c r="L50" s="14"/>
+      <c r="M50" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="N50" s="16"/>
-      <c r="O50" s="16" t="s">
+      <c r="N50" s="14"/>
+      <c r="O50" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="P50" s="16"/>
-      <c r="Q50" s="16" t="s">
+      <c r="P50" s="14"/>
+      <c r="Q50" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="R50" s="16"/>
-      <c r="S50" s="16" t="s">
+      <c r="R50" s="14"/>
+      <c r="S50" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="T50" s="16"/>
+      <c r="T50" s="14"/>
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
@@ -3983,11 +3983,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="M47:R47"/>
-    <mergeCell ref="M48:R49"/>
-    <mergeCell ref="M50:N50"/>
-    <mergeCell ref="O50:P50"/>
-    <mergeCell ref="Q50:R50"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="I1:J1"/>
@@ -4004,6 +3999,11 @@
     <mergeCell ref="I50:J50"/>
     <mergeCell ref="K50:L50"/>
     <mergeCell ref="G47:L47"/>
+    <mergeCell ref="M47:R47"/>
+    <mergeCell ref="M48:R49"/>
+    <mergeCell ref="M50:N50"/>
+    <mergeCell ref="O50:P50"/>
+    <mergeCell ref="Q50:R50"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4015,38 +4015,38 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="18" t="s">
+      <c r="B1" s="18"/>
+      <c r="C1" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="19"/>
-      <c r="E1" s="21" t="s">
+      <c r="D1" s="18"/>
+      <c r="E1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="21"/>
-      <c r="G1" s="18" t="s">
+      <c r="F1" s="20"/>
+      <c r="G1" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="19"/>
-      <c r="I1" s="18" t="s">
+      <c r="H1" s="18"/>
+      <c r="I1" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="19"/>
-      <c r="K1" s="21" t="s">
+      <c r="J1" s="18"/>
+      <c r="K1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="21"/>
-      <c r="M1" s="18" t="s">
+      <c r="L1" s="20"/>
+      <c r="M1" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="19"/>
-      <c r="O1" s="20" t="s">
+      <c r="N1" s="18"/>
+      <c r="O1" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="15"/>
+      <c r="P1" s="16"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -4091,10 +4091,10 @@
       <c r="N2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="O2" s="20" t="s">
+      <c r="O2" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="15"/>
+      <c r="P2" s="16"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
@@ -6134,14 +6134,14 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14" t="s">
+      <c r="B7" s="21"/>
+      <c r="C7" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="14"/>
+      <c r="D7" s="21"/>
       <c r="F7">
         <v>65.5</v>
       </c>
@@ -6153,14 +6153,14 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14" t="s">
+      <c r="B8" s="21"/>
+      <c r="C8" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="14"/>
+      <c r="D8" s="21"/>
       <c r="G8">
         <v>31.5</v>
       </c>
@@ -6169,12 +6169,12 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
       <c r="F9">
         <v>158.19999999999999</v>
       </c>
@@ -6186,11 +6186,11 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
